--- a/output/pdf_financials_xlsx/FOR.xlsx
+++ b/output/pdf_financials_xlsx/FOR.xlsx
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.07838299999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.491402</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.053043</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.107911</v>
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.07838299999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.491402</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.053043</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.107911</v>
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.323373</v>
+        <v>0.24499</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.526013</v>
+        <v>0.034611</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.082327</v>
+        <v>0.029284</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.01863</v>
@@ -6080,7 +6080,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.037742</v>
       </c>
@@ -7536,7 +7540,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">

--- a/output/pdf_financials_xlsx/FOR.xlsx
+++ b/output/pdf_financials_xlsx/FOR.xlsx
@@ -1466,19 +1466,19 @@
         <v>0.002842</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.005799</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.005356</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.004072</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.002859</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.002818</v>
       </c>
     </row>
     <row r="29">
@@ -1503,19 +1503,19 @@
         <v>-0.70722</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.827759</v>
+        <v>-1.82196</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.371331</v>
+        <v>-1.365975</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.43024</v>
+        <v>-1.426168</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.715429</v>
+        <v>-1.71257</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.167209</v>
+        <v>-1.164391</v>
       </c>
     </row>
     <row r="30">
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.005799</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.005356</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.004072</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.002859</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.002818</v>
       </c>
     </row>
     <row r="101">
@@ -4702,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -4711,13 +4711,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.021917</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.003572</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -8132,7 +8132,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -8662,7 +8666,11 @@
           <t>Proceeds on sale of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -9784,7 +9792,11 @@
           <t>Proceeds on sale of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -10894,7 +10906,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -12554,7 +12570,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FOR.xlsx
+++ b/output/pdf_financials_xlsx/FOR.xlsx
@@ -982,10 +982,10 @@
         <v>-0.710062</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-1.827759</v>
+        <v>-1.755501</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-1.371331</v>
+        <v>-1.177562</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-1.43024</v>
@@ -994,7 +994,7 @@
         <v>-1.715429</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-1.167209</v>
+        <v>-1.025762</v>
       </c>
     </row>
     <row r="17">
@@ -1019,10 +1019,10 @@
         <v>0.096223</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.072258</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.193769</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0.043498</v>
@@ -1031,7 +1031,7 @@
         <v>0.225926</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.141447</v>
       </c>
     </row>
     <row r="18">
@@ -1429,10 +1429,10 @@
         <v>-0.710062</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.827759</v>
+        <v>-1.755501</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.371331</v>
+        <v>-1.177562</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.43024</v>
@@ -1441,7 +1441,7 @@
         <v>-1.715429</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.167209</v>
+        <v>-1.025762</v>
       </c>
     </row>
     <row r="28">
@@ -1503,10 +1503,10 @@
         <v>-0.70722</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.82196</v>
+        <v>-1.749702</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.365975</v>
+        <v>-1.172206</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.426168</v>
@@ -1515,7 +1515,7 @@
         <v>-1.71257</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.164391</v>
+        <v>-1.022944</v>
       </c>
     </row>
     <row r="30">
@@ -1597,10 +1597,10 @@
         <v>-13.55135185378178</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.11608993671892</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-16.45509960409728</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-3.041307752545027</v>
@@ -1609,7 +1609,7 @@
         <v>-13.17023321862928</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-13.78945603366083</v>
       </c>
     </row>
     <row r="32">
@@ -2853,34 +2853,34 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.188601</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.145467</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.130697</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.10585</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.112576</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.170447</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.177404</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.1314</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.291039</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.609508</v>
       </c>
     </row>
     <row r="65">
@@ -4471,34 +4471,34 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-0.05912</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>0.200143</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>0.190709</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-0.055172</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>0.298832</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-0.235613</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-0.021471</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.245067</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>0.225125</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-0.591228</v>
       </c>
     </row>
     <row r="107">
@@ -4807,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.423452</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -8248,7 +8248,11 @@
           <t>Deferred income tax expense (recovery) (note 11)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -8502,7 +8506,11 @@
           <t>Net change in non-cash operating working capital (note 12)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -9282,7 +9290,11 @@
           <t>Deferred income tax expense (note 11)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -9602,7 +9614,11 @@
           <t>Deferred income tax expense (recovery) (note 10)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -9730,7 +9746,11 @@
           <t>Net change in non-cash operating working capital (note 11)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -10060,7 +10080,11 @@
           <t>Deferred income tax recovery (note 10)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -11038,7 +11062,11 @@
           <t>Gross proceeds received upon completion of private placement (note 10)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -11104,7 +11132,11 @@
           <t>Unit issuance costs associated with private placement (note 10)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -11562,7 +11594,11 @@
           <t>Net change in non-cash operating working capital (note 14)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -11626,7 +11662,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -11950,7 +11990,11 @@
           <t>Net change in non-cash operating working capital (note 13)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>-0.05912</v>
       </c>
@@ -13058,7 +13102,11 @@
           <t>Deferred income tax recovery (expense) (note 12)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -13890,7 +13938,11 @@
           <t>Deferred income tax recovery (expense) (note 10)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -14538,7 +14590,11 @@
           <t>Deferred income tax recovery (note 10)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
